--- a/consent_forms/039_hospital_staff_innovation_story_consent_form--consent_forms.xlsx
+++ b/consent_forms/039_hospital_staff_innovation_story_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Staff Innovation Story</t>
+          <t>Staff Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_2</t>
+          <t>innovation_story_title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Staff Title</t>
+          <t>Innovation Story Title</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_3</t>
+          <t>consent_to_share</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Permission To Share</t>
+          <t>Consent to Share</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_4</t>
+          <t>innovation_story_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_5</t>
+          <t>more_about_story</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Innovation Story</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>A brief description of your innovation story</t>
-        </is>
-      </c>
+          <t>More about the Story</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,22 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_6</t>
+          <t>staff_contact_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Innovation Story</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>More details about your innovation story</t>
-        </is>
-      </c>
+          <t>Staff Contact Information</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_7</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Innovation Story</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_8</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Innovation Story</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -712,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_9</t>
+          <t>innovation_story_consent_notes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Innovation Story</t>
+          <t>Consented Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -735,70 +727,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_10</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Staff Contact Information</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>staff_innovation_story_consent_form_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Staff Email Address</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Email address of the staff</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>staff_innovation_story_consent_form_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Staff Phone Number</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Phone number of the staff</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -815,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,32 +781,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_3_choices</t>
+          <t>staff_innovation_story_consent_form_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>manager/director</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Manager/Director</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>staff_innovation_story_consent_form_3_choices</t>
+          <t>staff_innovation_story_consent_form_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>clinical_specialist</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Clinical Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>staff_innovation_story_consent_form_1_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nurse</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>staff_innovation_story_consent_form_1_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Doctor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>staff_innovation_story_consent_form_1_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>consent_to_share_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>consent_to_share_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
